--- a/results/tables/01_contamination_assessment/table3_rda_predictor_terms.xlsx
+++ b/results/tables/01_contamination_assessment/table3_rda_predictor_terms.xlsx
@@ -470,19 +470,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3345408092469868</v>
+        <v>5.345823495689245</v>
       </c>
       <c r="D2" t="n">
-        <v>1.054502579803299</v>
+        <v>0.9285549089617862</v>
       </c>
       <c r="E2" t="n">
-        <v>0.384</v>
+        <v>0.521</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7060191891102724</v>
+        <v>0.1562118840329422</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02358517216352904</v>
+        <v>-0.3445935647798478</v>
       </c>
     </row>
     <row r="3">
@@ -495,19 +495,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.479467301529505</v>
+        <v>4.068346553668547</v>
       </c>
       <c r="D3" t="n">
-        <v>1.511323857714807</v>
+        <v>0.7066606607593638</v>
       </c>
       <c r="E3" t="n">
-        <v>0.144</v>
+        <v>0.723</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5997854689350373</v>
+        <v>-0.2645078173913537</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2667385683943135</v>
+        <v>0.2412876220070281</v>
       </c>
     </row>
     <row r="4">
@@ -520,19 +520,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3042052364330137</v>
+        <v>8.622188337001731</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9588821385658043</v>
+        <v>1.497650514045595</v>
       </c>
       <c r="E4" t="n">
-        <v>0.46</v>
+        <v>0.135</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08257618388156504</v>
+        <v>-0.6950051692544533</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5524264998742503</v>
+        <v>-0.01267268444440966</v>
       </c>
     </row>
     <row r="5">
@@ -545,19 +545,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.4402741614107861</v>
+        <v>11.28934807610342</v>
       </c>
       <c r="D5" t="n">
-        <v>1.387783571377816</v>
+        <v>1.960928860351864</v>
       </c>
       <c r="E5" t="n">
-        <v>0.186</v>
+        <v>0.046</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01637119931297617</v>
+        <v>-0.4626803675271905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3057208056338802</v>
+        <v>-0.707491126206016</v>
       </c>
     </row>
     <row r="6">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.4509615200987063</v>
+        <v>10.79869140283424</v>
       </c>
       <c r="D6" t="n">
-        <v>1.421471082725272</v>
+        <v>1.875703139198455</v>
       </c>
       <c r="E6" t="n">
-        <v>0.17</v>
+        <v>0.059</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4907780079810626</v>
+        <v>-0.1184089736871203</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2400523509939655</v>
+        <v>0.7568391747358357</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.2606589154584706</v>
+        <v>7.753689084732585</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8216202364619678</v>
+        <v>1.346794571125957</v>
       </c>
       <c r="E7" t="n">
-        <v>0.621</v>
+        <v>0.186</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4716157725474603</v>
+        <v>0.2109391710813615</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5280824498268407</v>
+        <v>0.398081154662333</v>
       </c>
     </row>
   </sheetData>
